--- a/skhynix/dist/20261029_SK海力士個股模型_v0.6.xlsx
+++ b/skhynix/dist/20261029_SK海力士個股模型_v0.6.xlsx
@@ -401,6 +401,7 @@
     <definedName function="false" hidden="false" name="q4_np_hi" vbProcedure="false">In!$F$11</definedName>
     <definedName function="false" hidden="false" name="q4_np_lo" vbProcedure="false">In!$D$11</definedName>
     <definedName function="false" hidden="false" name="rf" vbProcedure="false">In!$E$36</definedName>
+    <definedName function="false" hidden="false" name="rm_factor" vbProcedure="false">Val!$B$203</definedName>
     <definedName function="false" hidden="false" name="sh25" vbProcedure="false">In!$E$21</definedName>
     <definedName function="false" hidden="false" name="sh25_hi" vbProcedure="false">In!$F$21</definedName>
     <definedName function="false" hidden="false" name="sh25_lo" vbProcedure="false">In!$D$21</definedName>
@@ -420,6 +421,7 @@
     <definedName function="false" hidden="false" name="tax" vbProcedure="false">In!$E$35</definedName>
     <definedName function="false" hidden="false" name="tax_hi" vbProcedure="false">In!$F$35</definedName>
     <definedName function="false" hidden="false" name="tax_lo" vbProcedure="false">In!$D$35</definedName>
+    <definedName function="false" hidden="false" name="tp_comp_adj" vbProcedure="false">Val!$B$204</definedName>
     <definedName function="false" hidden="false" name="tp_g" vbProcedure="false">In!$E$246</definedName>
     <definedName function="false" hidden="false" name="tp_r" vbProcedure="false">In!$E$245</definedName>
     <definedName function="false" hidden="false" name="tp_roe" vbProcedure="false">In!$E$247</definedName>
@@ -503,7 +505,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2043" uniqueCount="1073">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2096" uniqueCount="1112">
   <si>
     <r>
       <rPr>
@@ -4079,45 +4081,45 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：目標價 ₩</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3,408,692</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DCF 4,288,814</t>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：情境分歧集中在 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年後：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">EPS 2028 A 818,444</t>
     </r>
     <r>
       <rPr>
@@ -4136,83 +4138,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Comparable 2,528,569 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">各半），比現價 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1,277,000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-10-23</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）高 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">166.9%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，級距 大於 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">50%</t>
+      <t xml:space="preserve">B 375,667</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C 222,213</t>
     </r>
     <r>
       <rPr>
@@ -4231,6 +4176,570 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">DCF </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">情境價值（推到 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月後）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A 7,641,482</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B 3,401,631</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C 1,477,771</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">情境為現價 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.16 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">倍。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年淨利 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">264 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">兆幾乎不變：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3Q </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">業外淨損 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">32.6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">兆（匯兌損失 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11.6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、投資資產評價損失 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">22.9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、其他淨收益 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）抵銷了 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4Q </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">上調。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">重點觀察 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027 A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營業利益對一般 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DRAM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收入最敏感（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">±20% → ±13.7%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NAND ±30% → ±8.3%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HBM ±30% → ±5.4%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。待校正：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3Q </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資產負債表（權益、股數為推估，假設 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">40 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">兆買回於 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3Q </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">執行完畢）於季報公布後更新；下一個檢驗事件是 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4Q26 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">財報（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027-01 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">下旬）的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DRAM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">位元與 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HBM4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">占比。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-29</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：加權目標價中的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">Comparable </t>
     </r>
     <r>
@@ -4240,398 +4749,178 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">單獨為 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+98.0%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">v0.6 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">滾入 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3Q26 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">實績與 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4Q </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">指引（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DRAM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">位元季增中 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20% </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">段）後，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年第四季營收由 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">113.1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">升到 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">140.7 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">兆，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">起各年營收隨第四季基期上移約 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9–10%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年度股利（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">支付）依公司「全年現金股利 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">30 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">兆以上」改為每股 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">22,050 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">韓元後，同樣的股東回饋總額中買回減少、股數多約 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.2%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，加權目標價合計 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+10.4%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">。上檔空間仍主要來自倍數：現價隱含約 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.0 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">倍前瞻 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">P/B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，同業中位數 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.94 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">倍。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">重點觀察 </t>
+      <t xml:space="preserve">改用相對倍數調整後的值（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Val </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">節：同業前瞻倍數中位數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本公司 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年相對同業的倍數比，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">前瞻倍數；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Andy 2026-10-27</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「照建議做」、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10-29 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資料取回）。「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Comparable </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目標價（市場主流同業法）」維持不調整。重點觀察 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的第一句已改為公式；重點觀察 </t>
     </r>
     <r>
       <rPr>
@@ -4650,44 +4939,6 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">：情境分歧集中在 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2028 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年後：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">EPS 2028 A 818,444</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">、</t>
     </r>
     <r>
@@ -4698,578 +4949,35 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">B 375,667</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C 222,213</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DCF </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">情境價值（推到 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">個月後）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A 7,641,482</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B 3,401,631</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C 1,477,771</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">情境為現價 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.16 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">倍。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年淨利 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">264 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">兆幾乎不變：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3Q </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">業外淨損 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">32.6 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">兆（匯兌損失 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">11.6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、投資資產評價損失 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">22.9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、其他淨收益 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）抵銷了 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4Q </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">上調。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">重點觀察 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027 A </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營業利益對一般 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DRAM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收入最敏感（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">±20% → ±13.7%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">），</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">NAND ±30% → ±8.3%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HBM ±30% → ±5.4%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">。待校正：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3Q </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">資產負債表（權益、股數為推估，假設 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">40 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">兆買回於 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3Q </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">執行完畢）於季報公布後更新；下一個檢驗事件是 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4Q26 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">財報（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2027-01 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">下旬）的 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DRAM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">位元與 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HBM4 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">占比。</t>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">與其他說明中的目標價與上檔空間數字為調整前撰寫，以 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Val </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">頁為準。</t>
     </r>
   </si>
   <si>
@@ -36845,116 +36553,13 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Sens — </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">一次只動一個價格或份額輸入；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Δ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營業利益＝</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Δ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營收 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× (1 − </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">營業費用變動率</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（成本只隨量變動，所以這是精確值，不是近似）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">欄</t>
-  </si>
-  <si>
-    <t xml:space="preserve">輸入變動</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
         <b val="true"/>
         <sz val="11"/>
         <rFont val="Cambria"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Δ</t>
+      <t xml:space="preserve">0.5 </t>
     </r>
     <r>
       <rPr>
@@ -36963,324 +36568,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">營收</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">營業利益</t>
-  </si>
-  <si>
-    <t xml:space="preserve">相對基準</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">一般 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DRAM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收入 −</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">一般 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DRAM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收入 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+20%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HBM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收入 −</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">30%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（價格或份額）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">HBM </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收入 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+30%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">NAND </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收入 −</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">30%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">NAND </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收入 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+30%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">讀法：哪一條收入線的同幅變動對營業利益影響最大，就是該年度的主要驅動。價格路徑本身的情境差異見 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Y </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">頁 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">欄。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">目標價參數（只改 </t>
+      <t xml:space="preserve">相對倍數調整（</t>
     </r>
     <r>
       <rPr>
@@ -37290,7 +36578,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">DCF </t>
+      <t xml:space="preserve">Comparable </t>
     </r>
     <r>
       <rPr>
@@ -37299,7 +36587,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">參數；</t>
+      <t xml:space="preserve">目標倍數＝同業中位數 </t>
     </r>
     <r>
       <rPr>
@@ -37309,7 +36597,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Y </t>
+      <t xml:space="preserve">× </t>
     </r>
     <r>
       <rPr>
@@ -37318,7 +36606,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">頁收斂法的 </t>
+      <t xml:space="preserve">本公司 </t>
     </r>
     <r>
       <rPr>
@@ -37328,7 +36616,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">fade_g </t>
+      <t xml:space="preserve">10 </t>
     </r>
     <r>
       <rPr>
@@ -37337,7 +36625,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">不隨 </t>
+      <t xml:space="preserve">年相對同業的 </t>
     </r>
     <r>
       <rPr>
@@ -37347,7 +36635,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tp_g </t>
+      <t xml:space="preserve">P/B </t>
     </r>
     <r>
       <rPr>
@@ -37356,16 +36644,8 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">變動）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">案例</t>
-  </si>
-  <si>
-    <t xml:space="preserve">設定</t>
-  </si>
-  <si>
+      <t xml:space="preserve">比；</t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
@@ -37374,7 +36654,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">DCF </t>
+      <t xml:space="preserve">Andy 2026-10-27 </t>
     </r>
     <r>
       <rPr>
@@ -37383,8 +36663,343 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">目標價</t>
-    </r>
+      <t xml:space="preserve">新增，放在本頁最後以免位移既有儲存格）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資料：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2017–2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">各年度窗口（前一年 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月～當年 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月底前瞻 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）的中位數（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">tools/data/fwd_mult_hist.csv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Verified] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">來源、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Derived] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">彙總；有效值 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0 &lt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">值 ≤ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，無效值以「剔除</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」文字列示、不進中位數。本公司或同業有效年數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&lt; 7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不納入；有效同業 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&lt; 2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">家或本公司不足時係數＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（不調整）。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">公司</t>
+  </si>
+  <si>
+    <t xml:space="preserve">角色</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016/11–2017/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017/11–2018/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018/11–2019/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019/11–2020/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020/11–2021/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021/11–2022/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022/11–2023/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023/11–2024/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024/11–2025/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11–2026/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">有效年數</t>
   </si>
   <si>
     <r>
@@ -37395,7 +37010,1214 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年中位數</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">納入值</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SK </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">海力士</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">000660.KS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本公司</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg 000660 KS Equity BEST_PX_BPS_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">同業</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg 005930 KS Equity BEST_PX_BPS_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg MU US Equity BEST_PX_BPS_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg 285A JT Equity BEST_PX_BPS_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg 2408 TT Equity BEST_PX_BPS_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本公司 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年中位數（納入值）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">空白＝本公司有效年數不足</t>
+  </si>
+  <si>
+    <t xml:space="preserve">納入的同業家數</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同業 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年中位數的中位數</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">原始比值（本公司 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同業）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝本公司長期比同業便宜（折價），＞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝長期溢價</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">夾值下限</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Assumed] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">避免單一歷史異常主導；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">tools/relative_multiple.py </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RM_LO</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">夾值上限</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Assumed] tools/relative_multiple.py </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RM_HI</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">相對倍數調整係數</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資料不足時＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（不調整）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">Comparable </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目標價（相對倍數調整後）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Comparable </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目標價（市場主流同業法）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">調整係數；加權目標價使用本列</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Sens — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">一次只動一個價格或份額輸入；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Δ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營業利益＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Δ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營收 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× (1 − </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營業費用變動率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（成本只隨量變動，所以這是精確值，不是近似）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">欄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">輸入變動</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Δ</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">營收</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">營業利益</t>
+  </si>
+  <si>
+    <t xml:space="preserve">相對基準</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">一般 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DRAM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收入 −</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">一般 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DRAM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收入 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+20%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HBM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收入 −</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（價格或份額）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HBM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收入 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+30%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NAND </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收入 −</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NAND </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收入 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+30%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">讀法：哪一條收入線的同幅變動對營業利益影響最大，就是該年度的主要驅動。價格路徑本身的情境差異見 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Y </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">頁 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">欄。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目標價參數（只改 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DCF </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">參數；</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Y </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">頁收斂法的 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">fade_g </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不隨 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">tp_g </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">變動）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">案例</t>
+  </si>
+  <si>
+    <t xml:space="preserve">設定</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DCF </t>
     </r>
     <r>
       <rPr>
@@ -39481,7 +40303,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -39591,6 +40413,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -39850,7 +40676,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="170"/>
@@ -39992,17 +40818,23 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="s">
-        <v>24</v>
+      <c r="A29" s="0" t="str">
+        <f aca="false">"重點觀察 1：目標價 ₩"&amp;TEXT(Val!$B$161,"#,##0")&amp;"（DCF "&amp;TEXT(Val!$B$146,"#,##0")&amp;"、Comparable（相對倍數調整後）"&amp;TEXT(tp_comp_adj,"#,##0")&amp;"；DCF 權重 "&amp;TEXT(tp_w_dcf,"0%")&amp;"），比現價 "&amp;TEXT(px,"#,##0")&amp;"（2026-10-23）"&amp;IF(Val!$B$164&gt;=0,"高 "&amp;TEXT(Val!$B$164,"0.0%"),"低 "&amp;TEXT(-Val!$B$164,"0.0%"))&amp;"，級距 "&amp;Val!$B$184&amp;"、投資建議 "&amp;Val!$B$185&amp;"。相對倍數調整係數 "&amp;TEXT(rm_factor,"0.00")&amp;"（本公司 10 年前瞻倍數中位數 ÷ 同業的中位數，夾在 0.5–2.0；Val 第 0.5 節），調整前加權上檔空間 "&amp;TEXT((tp_w_dcf*Val!$B$146+(1-tp_w_dcf)*Val!$B$156)/px-1,"+0.0%;−0.0%")&amp;"；Comparable 單獨（市場主流同業法、未調整）為 "&amp;TEXT(Val!$B$165,"+0.0%;−0.0%")&amp;"。"&amp;"以下為 2026-10-29 相對倍數調整前撰寫的說明，其中數字為調整前：v0.6 滾入 3Q26 實績與 4Q 指引（DRAM 位元季增中 20% 段）後，2026 年第四季營收由 113.1 升到 140.7 兆，2027 起各年營收隨第四季基期上移約 9–10%；FY2026 年度股利（2027 支付）依公司「全年現金股利 30 兆以上」改為每股 22,050 韓元後，同樣的股東回饋總額中買"&amp;"回減少、股數多約 1.2%，加權目標價合計 +10.4%。上檔空間仍主要來自倍數：現價隱含約 1.0 倍前瞻 P/B，同業中位數 1.94 倍。"</f>
+        <v>重點觀察 1：目標價 ₩3,362,856（DCF 4,288,814、Comparable（相對倍數調整後）2,436,897；DCF 權重 50%），比現價 1,277,000（2026-10-23）高 163.3%，級距 大於 50%、投資建議 強力買進。相對倍數調整係數 0.96（本公司 10 年前瞻倍數中位數 ÷ 同業的中位數，夾在 0.5–2.0；Val 第 0.5 節），調整前加權上檔空間 +166.9%；Comparable 單獨（市場主流同業法、未調整）為 +98.0%。以下為 2026-10-29 相對倍數調整前撰寫的說明，其中數字為調整前：v0.6 滾入 3Q26 實績與 4Q 指引（DRAM 位元季增中 20% 段）後，2026 年第四季營收由 113.1 升到 140.7 兆，2027 起各年營收隨第四季基期上移約 9–10%；FY2026 年度股利（2027 支付）依公司「全年現金股利 30 兆以上」改為每股 22,050 韓元後，同樣的股東回饋總額中買回減少、股數多約 1.2%，加權目標價合計 +10.4%。上檔空間仍主要來自倍數：現價隱含約 1.0 倍前瞻 P/B，同業中位數 1.94 倍。</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
         <v>26</v>
       </c>
     </row>
@@ -40031,12 +40863,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1037</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>1038</v>
+        <v>1077</v>
       </c>
       <c r="B3" s="0" t="n">
         <f aca="false">nv_hbm</f>
@@ -40048,7 +40880,7 @@
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>1039</v>
+        <v>1078</v>
       </c>
       <c r="B4" s="0" t="str">
         <f aca="false">TEXT(Mkt!D16,"0")&amp;" ／ "&amp;TEXT(Mkt!E16,"0")</f>
@@ -40060,7 +40892,7 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>1040</v>
+        <v>1079</v>
       </c>
       <c r="B5" s="0" t="str">
         <f aca="false">TEXT(Mkt!D33,"0")&amp;" ／ "&amp;TEXT(Mkt!E33,"0")</f>
@@ -40072,7 +40904,7 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>1041</v>
+        <v>1080</v>
       </c>
       <c r="B6" s="14" t="n">
         <f aca="false">Mkt!E27</f>
@@ -40084,10 +40916,10 @@
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>1042</v>
+        <v>1081</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>1043</v>
+        <v>1082</v>
       </c>
       <c r="C7" s="0" t="s">
         <v>153</v>
@@ -40123,122 +40955,122 @@
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>1044</v>
+        <v>1083</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>1045</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>1046</v>
+        <v>1085</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>1047</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>1048</v>
+        <v>1087</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>1049</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>1050</v>
+        <v>1089</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>1051</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>1052</v>
+        <v>1091</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>1053</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>1054</v>
+        <v>1093</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>1055</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>1056</v>
+        <v>1095</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>1057</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>1058</v>
+        <v>1097</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>1059</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>1060</v>
+        <v>1099</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>1061</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>1062</v>
+        <v>1101</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>1063</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>1064</v>
+        <v>1103</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>1065</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>1066</v>
+        <v>1105</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>1067</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>1068</v>
+        <v>1107</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>1069</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>1070</v>
+        <v>1109</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>1071</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>1072</v>
+        <v>1111</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>1071</v>
+        <v>1110</v>
       </c>
     </row>
   </sheetData>
@@ -49915,7 +50747,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H185"/>
+  <dimension ref="A1:Q204"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36"/>
@@ -52774,8 +53606,8 @@
         <v>945</v>
       </c>
       <c r="B161" s="25" t="n">
-        <f aca="false">tp_w_dcf*B146+(1-tp_w_dcf)*B156</f>
-        <v>3408691.72663474</v>
+        <f aca="false">tp_w_dcf*B146+(1-tp_w_dcf)*tp_comp_adj</f>
+        <v>3362855.89676401</v>
       </c>
       <c r="E161" s="8" t="s">
         <v>946</v>
@@ -52808,7 +53640,7 @@
       </c>
       <c r="B164" s="19" t="n">
         <f aca="false">B161/px-1</f>
-        <v>1.66929657528171</v>
+        <v>1.6334032081159</v>
       </c>
       <c r="E164" s="5" t="s">
         <v>950</v>
@@ -53050,6 +53882,413 @@
       </c>
       <c r="E185" s="5" t="s">
         <v>977</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="1" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="5" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="6" t="s">
+        <v>980</v>
+      </c>
+      <c r="B190" s="6" t="s">
+        <v>917</v>
+      </c>
+      <c r="C190" s="6" t="s">
+        <v>981</v>
+      </c>
+      <c r="D190" s="13" t="s">
+        <v>982</v>
+      </c>
+      <c r="E190" s="13" t="s">
+        <v>983</v>
+      </c>
+      <c r="F190" s="13" t="s">
+        <v>984</v>
+      </c>
+      <c r="G190" s="13" t="s">
+        <v>985</v>
+      </c>
+      <c r="H190" s="13" t="s">
+        <v>986</v>
+      </c>
+      <c r="I190" s="13" t="s">
+        <v>987</v>
+      </c>
+      <c r="J190" s="13" t="s">
+        <v>988</v>
+      </c>
+      <c r="K190" s="13" t="s">
+        <v>989</v>
+      </c>
+      <c r="L190" s="13" t="s">
+        <v>990</v>
+      </c>
+      <c r="M190" s="13" t="s">
+        <v>991</v>
+      </c>
+      <c r="N190" s="6" t="s">
+        <v>992</v>
+      </c>
+      <c r="O190" s="13" t="s">
+        <v>993</v>
+      </c>
+      <c r="P190" s="6" t="s">
+        <v>994</v>
+      </c>
+      <c r="Q190" s="6" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="0" t="s">
+        <v>995</v>
+      </c>
+      <c r="B191" s="0" t="s">
+        <v>996</v>
+      </c>
+      <c r="C191" s="5" t="s">
+        <v>997</v>
+      </c>
+      <c r="D191" s="18" t="n">
+        <v>1.213</v>
+      </c>
+      <c r="E191" s="18" t="n">
+        <v>1.1395</v>
+      </c>
+      <c r="F191" s="18" t="n">
+        <v>0.9995</v>
+      </c>
+      <c r="G191" s="18" t="n">
+        <v>1.091</v>
+      </c>
+      <c r="H191" s="18" t="n">
+        <v>1.373</v>
+      </c>
+      <c r="I191" s="18" t="n">
+        <v>1.011</v>
+      </c>
+      <c r="J191" s="18" t="n">
+        <v>1.2725</v>
+      </c>
+      <c r="K191" s="18" t="n">
+        <v>1.6605</v>
+      </c>
+      <c r="L191" s="18" t="n">
+        <v>1.3995</v>
+      </c>
+      <c r="M191" s="18" t="n">
+        <v>2.3405</v>
+      </c>
+      <c r="N191" s="8" t="n">
+        <f aca="false">COUNT(D191:M191)</f>
+        <v>10</v>
+      </c>
+      <c r="O191" s="14" t="n">
+        <f aca="false">IF(N191&gt;0,MEDIAN(D191:M191),"")</f>
+        <v>1.24275</v>
+      </c>
+      <c r="P191" s="14" t="n">
+        <f aca="false">IF(N191&gt;=7,O191,"")</f>
+        <v>1.24275</v>
+      </c>
+      <c r="Q191" s="8" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="5" t="s">
+        <v>921</v>
+      </c>
+      <c r="B192" s="0" t="s">
+        <v>922</v>
+      </c>
+      <c r="C192" s="5" t="s">
+        <v>999</v>
+      </c>
+      <c r="D192" s="18" t="n">
+        <v>1.4135</v>
+      </c>
+      <c r="E192" s="18" t="n">
+        <v>1.2645</v>
+      </c>
+      <c r="F192" s="18" t="n">
+        <v>1.152</v>
+      </c>
+      <c r="G192" s="18" t="n">
+        <v>1.279</v>
+      </c>
+      <c r="H192" s="18" t="n">
+        <v>1.7855</v>
+      </c>
+      <c r="I192" s="18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J192" s="18" t="n">
+        <v>1.219</v>
+      </c>
+      <c r="K192" s="18" t="n">
+        <v>1.303</v>
+      </c>
+      <c r="L192" s="18" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="M192" s="18" t="n">
+        <v>1.8275</v>
+      </c>
+      <c r="N192" s="8" t="n">
+        <f aca="false">COUNT(D192:M192)</f>
+        <v>10</v>
+      </c>
+      <c r="O192" s="14" t="n">
+        <f aca="false">IF(N192&gt;0,MEDIAN(D192:M192),"")</f>
+        <v>1.2895</v>
+      </c>
+      <c r="P192" s="14" t="n">
+        <f aca="false">IF(N192&gt;=7,O192,"")</f>
+        <v>1.2895</v>
+      </c>
+      <c r="Q192" s="8" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="5" t="s">
+        <v>925</v>
+      </c>
+      <c r="B193" s="0" t="s">
+        <v>926</v>
+      </c>
+      <c r="C193" s="5" t="s">
+        <v>999</v>
+      </c>
+      <c r="D193" s="18" t="n">
+        <v>1.584</v>
+      </c>
+      <c r="E193" s="18" t="n">
+        <v>1.503</v>
+      </c>
+      <c r="F193" s="18" t="n">
+        <v>1.2295</v>
+      </c>
+      <c r="G193" s="18" t="n">
+        <v>1.3335</v>
+      </c>
+      <c r="H193" s="18" t="n">
+        <v>1.802</v>
+      </c>
+      <c r="I193" s="18" t="n">
+        <v>1.306</v>
+      </c>
+      <c r="J193" s="18" t="n">
+        <v>1.656</v>
+      </c>
+      <c r="K193" s="18" t="n">
+        <v>2.1515</v>
+      </c>
+      <c r="L193" s="18" t="n">
+        <v>1.898</v>
+      </c>
+      <c r="M193" s="18" t="n">
+        <v>3.5655</v>
+      </c>
+      <c r="N193" s="8" t="n">
+        <f aca="false">COUNT(D193:M193)</f>
+        <v>10</v>
+      </c>
+      <c r="O193" s="14" t="n">
+        <f aca="false">IF(N193&gt;0,MEDIAN(D193:M193),"")</f>
+        <v>1.62</v>
+      </c>
+      <c r="P193" s="14" t="n">
+        <f aca="false">IF(N193&gt;=7,O193,"")</f>
+        <v>1.62</v>
+      </c>
+      <c r="Q193" s="8" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="5" t="s">
+        <v>928</v>
+      </c>
+      <c r="B194" s="0" t="s">
+        <v>929</v>
+      </c>
+      <c r="C194" s="5" t="s">
+        <v>999</v>
+      </c>
+      <c r="L194" s="18" t="n">
+        <v>1.494</v>
+      </c>
+      <c r="M194" s="18" t="n">
+        <v>3.9425</v>
+      </c>
+      <c r="N194" s="8" t="n">
+        <f aca="false">COUNT(D194:M194)</f>
+        <v>2</v>
+      </c>
+      <c r="O194" s="14" t="n">
+        <f aca="false">IF(N194&gt;0,MEDIAN(D194:M194),"")</f>
+        <v>2.71825</v>
+      </c>
+      <c r="P194" s="14" t="str">
+        <f aca="false">IF(N194&gt;=7,O194,"")</f>
+        <v/>
+      </c>
+      <c r="Q194" s="8" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="5" t="s">
+        <v>932</v>
+      </c>
+      <c r="B195" s="0" t="s">
+        <v>933</v>
+      </c>
+      <c r="C195" s="5" t="s">
+        <v>999</v>
+      </c>
+      <c r="D195" s="18" t="n">
+        <v>1.4325</v>
+      </c>
+      <c r="E195" s="18" t="n">
+        <v>1.537</v>
+      </c>
+      <c r="F195" s="18" t="n">
+        <v>1.203</v>
+      </c>
+      <c r="G195" s="18" t="n">
+        <v>1.1455</v>
+      </c>
+      <c r="H195" s="18" t="n">
+        <v>1.3955</v>
+      </c>
+      <c r="I195" s="18" t="n">
+        <v>1.0635</v>
+      </c>
+      <c r="J195" s="18" t="n">
+        <v>1.195</v>
+      </c>
+      <c r="K195" s="18" t="n">
+        <v>1.1785</v>
+      </c>
+      <c r="L195" s="18" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="M195" s="18" t="n">
+        <v>2.7665</v>
+      </c>
+      <c r="N195" s="8" t="n">
+        <f aca="false">COUNT(D195:M195)</f>
+        <v>10</v>
+      </c>
+      <c r="O195" s="14" t="n">
+        <f aca="false">IF(N195&gt;0,MEDIAN(D195:M195),"")</f>
+        <v>1.199</v>
+      </c>
+      <c r="P195" s="14" t="n">
+        <f aca="false">IF(N195&gt;=7,O195,"")</f>
+        <v>1.199</v>
+      </c>
+      <c r="Q195" s="8" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="5" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B197" s="14" t="n">
+        <f aca="false">P191</f>
+        <v>1.24275</v>
+      </c>
+      <c r="E197" s="5" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="5" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B198" s="16" t="n">
+        <f aca="false">COUNT(P192:P195)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="5" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B199" s="14" t="n">
+        <f aca="false">IF(B198&gt;0,MEDIAN(P192:P195),"")</f>
+        <v>1.2895</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="5" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B200" s="14" t="n">
+        <f aca="false">IF(AND(ISNUMBER(B197),B198&gt;=2),B197/B199,"")</f>
+        <v>0.963745637844126</v>
+      </c>
+      <c r="E200" s="5" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="5" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B201" s="18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E201" s="8" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="5" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B202" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E202" s="8" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="3" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B203" s="28" t="n">
+        <f aca="false">IF(ISNUMBER(B200),MIN(MAX(B200,B201),B202),1)</f>
+        <v>0.963745637844126</v>
+      </c>
+      <c r="E203" s="5" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B204" s="25" t="n">
+        <f aca="false">Val!$B$156*B203</f>
+        <v>2436897.43622891</v>
+      </c>
+      <c r="E204" s="5" t="s">
+        <v>1017</v>
       </c>
     </row>
   </sheetData>
@@ -53077,24 +54316,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>978</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>979</v>
+        <v>1019</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>980</v>
+        <v>1020</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>981</v>
+        <v>1021</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>982</v>
+        <v>1022</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>983</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53114,7 +54353,7 @@
         <v>766</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>984</v>
+        <v>1024</v>
       </c>
       <c r="C5" s="17" t="n">
         <f aca="false">-0.2*Y!D5</f>
@@ -53134,7 +54373,7 @@
         <v>766</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>985</v>
+        <v>1025</v>
       </c>
       <c r="C6" s="17" t="n">
         <f aca="false">0.2*Y!D5</f>
@@ -53154,7 +54393,7 @@
         <v>766</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>986</v>
+        <v>1026</v>
       </c>
       <c r="C7" s="17" t="n">
         <f aca="false">-0.3*Y!D6</f>
@@ -53174,7 +54413,7 @@
         <v>766</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>987</v>
+        <v>1027</v>
       </c>
       <c r="C8" s="17" t="n">
         <f aca="false">0.3*Y!D6</f>
@@ -53194,7 +54433,7 @@
         <v>766</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>988</v>
+        <v>1028</v>
       </c>
       <c r="C9" s="17" t="n">
         <f aca="false">-0.3*Y!D7</f>
@@ -53214,7 +54453,7 @@
         <v>766</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>989</v>
+        <v>1029</v>
       </c>
       <c r="C10" s="17" t="n">
         <f aca="false">0.3*Y!D7</f>
@@ -53246,7 +54485,7 @@
         <v>770</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>984</v>
+        <v>1024</v>
       </c>
       <c r="C13" s="17" t="n">
         <f aca="false">-0.2*Y!H5</f>
@@ -53266,7 +54505,7 @@
         <v>770</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>985</v>
+        <v>1025</v>
       </c>
       <c r="C14" s="17" t="n">
         <f aca="false">0.2*Y!H5</f>
@@ -53286,7 +54525,7 @@
         <v>770</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>986</v>
+        <v>1026</v>
       </c>
       <c r="C15" s="17" t="n">
         <f aca="false">-0.3*Y!H6</f>
@@ -53306,7 +54545,7 @@
         <v>770</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>987</v>
+        <v>1027</v>
       </c>
       <c r="C16" s="17" t="n">
         <f aca="false">0.3*Y!H6</f>
@@ -53326,7 +54565,7 @@
         <v>770</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>988</v>
+        <v>1028</v>
       </c>
       <c r="C17" s="17" t="n">
         <f aca="false">-0.3*Y!H7</f>
@@ -53346,7 +54585,7 @@
         <v>770</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>989</v>
+        <v>1029</v>
       </c>
       <c r="C18" s="17" t="n">
         <f aca="false">0.3*Y!H7</f>
@@ -53378,7 +54617,7 @@
         <v>773</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>984</v>
+        <v>1024</v>
       </c>
       <c r="C21" s="17" t="n">
         <f aca="false">-0.2*Y!K5</f>
@@ -53398,7 +54637,7 @@
         <v>773</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>985</v>
+        <v>1025</v>
       </c>
       <c r="C22" s="17" t="n">
         <f aca="false">0.2*Y!K5</f>
@@ -53418,7 +54657,7 @@
         <v>773</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>986</v>
+        <v>1026</v>
       </c>
       <c r="C23" s="17" t="n">
         <f aca="false">-0.3*Y!K6</f>
@@ -53438,7 +54677,7 @@
         <v>773</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>987</v>
+        <v>1027</v>
       </c>
       <c r="C24" s="17" t="n">
         <f aca="false">0.3*Y!K6</f>
@@ -53458,7 +54697,7 @@
         <v>773</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>988</v>
+        <v>1028</v>
       </c>
       <c r="C25" s="17" t="n">
         <f aca="false">-0.3*Y!K7</f>
@@ -53478,7 +54717,7 @@
         <v>773</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>989</v>
+        <v>1029</v>
       </c>
       <c r="C26" s="17" t="n">
         <f aca="false">0.3*Y!K7</f>
@@ -53510,7 +54749,7 @@
         <v>774</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>984</v>
+        <v>1024</v>
       </c>
       <c r="C29" s="17" t="n">
         <f aca="false">-0.2*Y!L5</f>
@@ -53530,7 +54769,7 @@
         <v>774</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>985</v>
+        <v>1025</v>
       </c>
       <c r="C30" s="17" t="n">
         <f aca="false">0.2*Y!L5</f>
@@ -53550,7 +54789,7 @@
         <v>774</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>986</v>
+        <v>1026</v>
       </c>
       <c r="C31" s="17" t="n">
         <f aca="false">-0.3*Y!L6</f>
@@ -53570,7 +54809,7 @@
         <v>774</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>987</v>
+        <v>1027</v>
       </c>
       <c r="C32" s="17" t="n">
         <f aca="false">0.3*Y!L6</f>
@@ -53590,7 +54829,7 @@
         <v>774</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>988</v>
+        <v>1028</v>
       </c>
       <c r="C33" s="17" t="n">
         <f aca="false">-0.3*Y!L7</f>
@@ -53610,7 +54849,7 @@
         <v>774</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>989</v>
+        <v>1029</v>
       </c>
       <c r="C34" s="17" t="n">
         <f aca="false">0.3*Y!L7</f>
@@ -53627,32 +54866,32 @@
     </row>
     <row r="36" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>990</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>991</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>992</v>
+        <v>1032</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>993</v>
+        <v>1033</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>994</v>
+        <v>1034</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>995</v>
+        <v>1016</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>996</v>
+        <v>1035</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>983</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53660,19 +54899,19 @@
         <v>32</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>997</v>
+        <v>1036</v>
       </c>
       <c r="C40" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+tp_r)^1+Val!B139/(1+tp_r)^2+Val!B140/(1+tp_r)^3+Val!B133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C138/(1+tp_r)^1+Val!C139/(1+tp_r)^2+Val!C140/(1+tp_r)^3+Val!C133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D138/(1+tp_r)^1+Val!D139/(1+tp_r)^2+Val!D140/(1+tp_r)^3+Val!D133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
         <v>4288814.35729911</v>
       </c>
       <c r="D40" s="21" t="n">
-        <f aca="false">Val!B156</f>
-        <v>2528569.09597037</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>2436897.43622891</v>
       </c>
       <c r="E40" s="21" t="n">
         <f aca="false">tp_w_dcf*C40+(1-tp_w_dcf)*D40</f>
-        <v>3408691.72663474</v>
+        <v>3362855.89676401</v>
       </c>
       <c r="F40" s="19" t="n">
         <f aca="false">E40/E$40-1</f>
@@ -53681,153 +54920,153 @@
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>998</v>
+        <v>1037</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>999</v>
+        <v>1038</v>
       </c>
       <c r="C41" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+(tp_r+0.01))^1+Val!B139/(1+(tp_r+0.01))^2+Val!B140/(1+(tp_r+0.01))^3+Val!B133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!B134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!B135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!B135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wB*(Val!C138/(1+(tp_r+0.01))^1+Val!C139/(1+(tp_r+0.01))^2+Val!C140/(1+(tp_r+0.01))^3+Val!C133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!C134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!C135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!C135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6)+tp_wC*(Val!D138/(1+(tp_r+0.01))^1+Val!D139/(1+(tp_r+0.01))^2+Val!D140/(1+(tp_r+0.01))^3+Val!D133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^4+Val!D134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^5+Val!D135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r+0.01))^6+Val!D135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^6))*(1+(tp_r+0.01))</f>
         <v>3848740.73561347</v>
       </c>
       <c r="D41" s="21" t="n">
-        <f aca="false">Val!B156</f>
-        <v>2528569.09597037</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>2436897.43622891</v>
       </c>
       <c r="E41" s="21" t="n">
         <f aca="false">tp_w_dcf*C41+(1-tp_w_dcf)*D41</f>
-        <v>3188654.91579192</v>
+        <v>3142819.08592119</v>
       </c>
       <c r="F41" s="19" t="n">
         <f aca="false">E41/E$40-1</f>
-        <v>-0.064551689765168</v>
+        <v>-0.0654315312929573</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>1000</v>
+        <v>1039</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>1001</v>
+        <v>1040</v>
       </c>
       <c r="C42" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+(tp_r-0.01))^1+Val!B139/(1+(tp_r-0.01))^2+Val!B140/(1+(tp_r-0.01))^3+Val!B133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!B134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!B135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!B135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wB*(Val!C138/(1+(tp_r-0.01))^1+Val!C139/(1+(tp_r-0.01))^2+Val!C140/(1+(tp_r-0.01))^3+Val!C133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!C134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!C135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!C135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6)+tp_wC*(Val!D138/(1+(tp_r-0.01))^1+Val!D139/(1+(tp_r-0.01))^2+Val!D140/(1+(tp_r-0.01))^3+Val!D133*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^4+Val!D134*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^5+Val!D135*(1-MIN(tp_g/tp_roe,0.8))/(1+(tp_r-0.01))^6+Val!D135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^6))*(1+(tp_r-0.01))</f>
         <v>4899375.00243779</v>
       </c>
       <c r="D42" s="21" t="n">
-        <f aca="false">Val!B156</f>
-        <v>2528569.09597037</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>2436897.43622891</v>
       </c>
       <c r="E42" s="21" t="n">
         <f aca="false">tp_w_dcf*C42+(1-tp_w_dcf)*D42</f>
-        <v>3713972.04920408</v>
+        <v>3668136.21933335</v>
       </c>
       <c r="F42" s="19" t="n">
         <f aca="false">E42/E$40-1</f>
-        <v>0.0895593814436049</v>
+        <v>0.0907800785823454</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>1002</v>
+        <v>1041</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>1003</v>
+        <v>1042</v>
       </c>
       <c r="C43" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+tp_r)^1+Val!B139/(1+tp_r)^2+Val!B140/(1+tp_r)^3+Val!B133*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B134*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B135*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B135*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wB*(Val!C138/(1+tp_r)^1+Val!C139/(1+tp_r)^2+Val!C140/(1+tp_r)^3+Val!C133*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C134*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C135*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C135*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6)+tp_wC*(Val!D138/(1+tp_r)^1+Val!D139/(1+tp_r)^2+Val!D140/(1+tp_r)^3+Val!D133*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D134*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D135*(1-MIN((tp_g+0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D135*(1-MIN((tp_g+0.01)/tp_roe,0.8))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^6))*(1+tp_r)</f>
         <v>4549899.93705935</v>
       </c>
       <c r="D43" s="21" t="n">
-        <f aca="false">Val!B156</f>
-        <v>2528569.09597037</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>2436897.43622891</v>
       </c>
       <c r="E43" s="21" t="n">
         <f aca="false">tp_w_dcf*C43+(1-tp_w_dcf)*D43</f>
-        <v>3539234.51651486</v>
+        <v>3493398.68664413</v>
       </c>
       <c r="F43" s="19" t="n">
         <f aca="false">E43/E$40-1</f>
-        <v>0.0382970360329415</v>
+        <v>0.0388190258184238</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>1004</v>
+        <v>1043</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>1005</v>
+        <v>1044</v>
       </c>
       <c r="C44" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+tp_r)^1+Val!B139/(1+tp_r)^2+Val!B140/(1+tp_r)^3+Val!B133*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!B134*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!B135*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!B135*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wB*(Val!C138/(1+tp_r)^1+Val!C139/(1+tp_r)^2+Val!C140/(1+tp_r)^3+Val!C133*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!C134*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!C135*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!C135*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6)+tp_wC*(Val!D138/(1+tp_r)^1+Val!D139/(1+tp_r)^2+Val!D140/(1+tp_r)^3+Val!D133*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^4+Val!D134*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^5+Val!D135*(1-MIN((tp_g-0.01)/tp_roe,0.8))/(1+tp_r)^6+Val!D135*(1-MIN((tp_g-0.01)/tp_roe,0.8))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^6))*(1+tp_r)</f>
         <v>4112146.3715764</v>
       </c>
       <c r="D44" s="21" t="n">
-        <f aca="false">Val!B156</f>
-        <v>2528569.09597037</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>2436897.43622891</v>
       </c>
       <c r="E44" s="21" t="n">
         <f aca="false">tp_w_dcf*C44+(1-tp_w_dcf)*D44</f>
-        <v>3320357.73377339</v>
+        <v>3274521.90390265</v>
       </c>
       <c r="F44" s="19" t="n">
         <f aca="false">E44/E$40-1</f>
-        <v>-0.0259143389738452</v>
+        <v>-0.0262675522154713</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>1006</v>
+        <v>1045</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>1007</v>
+        <v>1046</v>
       </c>
       <c r="C45" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+tp_r)^1+Val!B139/(1+tp_r)^2+Val!B140/(1+tp_r)^3+Val!B133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C138/(1+tp_r)^1+Val!C139/(1+tp_r)^2+Val!C140/(1+tp_r)^3+Val!C133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D138/(1+tp_r)^1+Val!D139/(1+tp_r)^2+Val!D140/(1+tp_r)^3+Val!D133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
         <v>4288814.35729911</v>
       </c>
       <c r="D45" s="21" t="n">
-        <f aca="false">Val!B156</f>
-        <v>2528569.09597037</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>2436897.43622891</v>
       </c>
       <c r="E45" s="21" t="n">
         <f aca="false">0.3*C45+(1-0.3)*D45</f>
-        <v>3056642.67436899</v>
+        <v>2992472.51254997</v>
       </c>
       <c r="F45" s="19" t="n">
         <f aca="false">E45/E$40-1</f>
-        <v>-0.103279815395132</v>
+        <v>-0.110139534843123</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>1008</v>
+        <v>1047</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>1009</v>
+        <v>1048</v>
       </c>
       <c r="C46" s="21" t="n">
         <f aca="false">(tp_wA*(Val!B138/(1+tp_r)^1+Val!B139/(1+tp_r)^2+Val!B140/(1+tp_r)^3+Val!B133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!B134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!B135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!B135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wB*(Val!C138/(1+tp_r)^1+Val!C139/(1+tp_r)^2+Val!C140/(1+tp_r)^3+Val!C133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!C134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!C135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!C135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6)+tp_wC*(Val!D138/(1+tp_r)^1+Val!D139/(1+tp_r)^2+Val!D140/(1+tp_r)^3+Val!D133*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^4+Val!D134*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^5+Val!D135*(1-MIN(tp_g/tp_roe,0.8))/(1+tp_r)^6+Val!D135*(1-MIN(tp_g/tp_roe,0.8))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^6))*(1+tp_r)</f>
         <v>4288814.35729911</v>
       </c>
       <c r="D46" s="21" t="n">
-        <f aca="false">Val!B156</f>
-        <v>2528569.09597037</v>
+        <f aca="false">tp_comp_adj</f>
+        <v>2436897.43622891</v>
       </c>
       <c r="E46" s="21" t="n">
         <f aca="false">0.7*C46+(1-0.7)*D46</f>
-        <v>3760740.77890049</v>
+        <v>3733239.28097805</v>
       </c>
       <c r="F46" s="19" t="n">
         <f aca="false">E46/E$40-1</f>
-        <v>0.103279815395132</v>
+        <v>0.110139534843123</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C47" s="28" t="n">
+        <v>1049</v>
+      </c>
+      <c r="C47" s="29" t="n">
         <f aca="false">C40-Val!B146</f>
         <v>0</v>
       </c>
@@ -53857,7 +55096,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>1011</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53865,21 +55104,21 @@
         <v>29</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>1012</v>
+        <v>1051</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1013</v>
+        <v>1052</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1014</v>
+        <v>1053</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>1015</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>1016</v>
+        <v>1055</v>
       </c>
       <c r="B4" s="17" t="n">
         <f aca="false">Y!C4</f>
@@ -53893,12 +55132,12 @@
         <v>0.0957791591226032</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>1017</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>1018</v>
+        <v>1057</v>
       </c>
       <c r="B5" s="17" t="n">
         <f aca="false">Y!C14</f>
@@ -53912,12 +55151,12 @@
         <v>0.116910997343893</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>1019</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>1020</v>
+        <v>1059</v>
       </c>
       <c r="B6" s="17" t="n">
         <f aca="false">Y!C20</f>
@@ -53931,12 +55170,12 @@
         <v>0.0297375053561129</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>1021</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>1022</v>
+        <v>1061</v>
       </c>
       <c r="B7" s="17" t="n">
         <f aca="false">Y!C6</f>
@@ -53950,12 +55189,12 @@
         <v>-0.107661421776805</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>1023</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>1024</v>
+        <v>1063</v>
       </c>
       <c r="B8" s="17" t="n">
         <f aca="false">Y!D4</f>
@@ -53969,12 +55208,12 @@
         <v>0.0977549358335661</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>1021</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>1025</v>
+        <v>1064</v>
       </c>
       <c r="B9" s="17" t="n">
         <f aca="false">Y!D14</f>
@@ -53988,12 +55227,12 @@
         <v>0.16268176396973</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>1026</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>1027</v>
+        <v>1066</v>
       </c>
       <c r="B10" s="17" t="n">
         <f aca="false">Y!D20</f>
@@ -54007,12 +55246,12 @@
         <v>0.117577469063303</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>1021</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>1028</v>
+        <v>1067</v>
       </c>
       <c r="B11" s="17" t="n">
         <f aca="false">Y!E14</f>
@@ -54026,12 +55265,12 @@
         <v>0.162482400914955</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>1029</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>1030</v>
+        <v>1069</v>
       </c>
       <c r="B12" s="17" t="n">
         <f aca="false">Q!H4</f>
@@ -54045,12 +55284,12 @@
         <v>0.111753453772582</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>1031</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>1032</v>
+        <v>1071</v>
       </c>
       <c r="B13" s="17" t="n">
         <f aca="false">Q!H10</f>
@@ -54064,12 +55303,12 @@
         <v>0.0950591327201054</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>1033</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>1034</v>
+        <v>1073</v>
       </c>
       <c r="B14" s="17" t="n">
         <f aca="false">Y!D29</f>
@@ -54089,7 +55328,7 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>1035</v>
+        <v>1074</v>
       </c>
       <c r="B15" s="17" t="n">
         <f aca="false">Y!E29</f>
@@ -54109,7 +55348,7 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>1036</v>
+        <v>1075</v>
       </c>
       <c r="B16" s="17" t="n">
         <f aca="false">Y!E28</f>
